--- a/output/pdf_financials_xlsx/SGC.xlsx
+++ b/output/pdf_financials_xlsx/SGC.xlsx
@@ -3655,28 +3655,28 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.505632</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.97024</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.233985</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.257228</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.708426</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.702421</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.714408</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.805919</v>
       </c>
     </row>
     <row r="93">
@@ -5932,7 +5932,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -7263,7 +7267,11 @@
           <t>Reserves 3,702,421</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -8081,7 +8089,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -8777,7 +8789,11 @@
           <t>Reserves 4, 8</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -9133,7 +9149,11 @@
           <t>Reserves 4, 7</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -9674,7 +9694,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SGC.xlsx
+++ b/output/pdf_financials_xlsx/SGC.xlsx
@@ -792,28 +792,28 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.035762</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.107277</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.030678</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.01007</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.01573</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.07618</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.026288</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.014795</v>
       </c>
     </row>
     <row r="13">
@@ -1348,28 +1348,28 @@
         <v>-0.001063</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.969331</v>
+        <v>-2.005093</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.761459</v>
+        <v>-0.868736</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.680782</v>
+        <v>-0.71146</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.416816</v>
+        <v>-0.426886</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.741586</v>
+        <v>-1.757316</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-3.516944</v>
+        <v>-3.593124</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.886481</v>
+        <v>-0.9127690000000001</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.148122</v>
+        <v>-1.162917</v>
       </c>
     </row>
     <row r="28">
@@ -1416,28 +1416,28 @@
         <v>-0.001063</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.969331</v>
+        <v>-2.005093</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.761459</v>
+        <v>-0.868736</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.680782</v>
+        <v>-0.71146</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.416816</v>
+        <v>-0.426886</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.741586</v>
+        <v>-1.757316</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-3.516944</v>
+        <v>-3.593124</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.886481</v>
+        <v>-0.9127690000000001</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.148122</v>
+        <v>-1.162917</v>
       </c>
     </row>
     <row r="30">
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>7.038129</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0</v>
@@ -1660,10 +1660,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>7.038129</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
@@ -21643,7 +21643,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -22540,7 +22540,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -24341,7 +24341,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -25295,7 +25295,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">

--- a/output/pdf_financials_xlsx/SGC.xlsx
+++ b/output/pdf_financials_xlsx/SGC.xlsx
@@ -622,28 +622,28 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.219266</v>
+        <v>0.260426</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.07327</v>
+        <v>0.123035</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.125326</v>
+        <v>0.145166</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.123135</v>
+        <v>0.142819</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.292453</v>
+        <v>0.329761</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.290547</v>
+        <v>0.359729</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.143429</v>
+        <v>0.174547</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.096313</v>
+        <v>0.114877</v>
       </c>
     </row>
     <row r="8">
@@ -739,7 +739,7 @@
         <v>5.644588</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.290547</v>
+        <v>0.359729</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0.993963</v>
@@ -773,7 +773,7 @@
         <v>-5.644588</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.290547</v>
+        <v>-0.359729</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>-0.993963</v>
@@ -962,10 +962,10 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0.208338</v>
+        <v>0.208338</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.028298</v>
+        <v>-0.028298</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -4425,13 +4425,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.038004</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.194807</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.019808</v>
       </c>
     </row>
     <row r="116">
@@ -10614,7 +10614,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -13693,7 +13697,11 @@
           <t>Proceeds from sale of marketable securities 38,004</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -21207,7 +21215,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -23042,7 +23054,11 @@
           <t>Office expenses 69,182</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -25474,7 +25490,11 @@
           <t>Deferred income tax recovery (expense) 7</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -25891,7 +25911,11 @@
           <t>Deferred income tax recovery (expense) 6</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
